--- a/artfynd/A 29919-2024 artfynd.xlsx
+++ b/artfynd/A 29919-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120306195</v>
       </c>
       <c r="B2" t="n">
-        <v>90846</v>
+        <v>90864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>120304151</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 29919-2024 artfynd.xlsx
+++ b/artfynd/A 29919-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120306195</v>
+        <v>120304151</v>
       </c>
       <c r="B2" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581432</v>
+        <v>581524</v>
       </c>
       <c r="R2" t="n">
-        <v>7025133</v>
+        <v>7024990</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120304151</v>
+        <v>120306195</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581524</v>
+        <v>581432</v>
       </c>
       <c r="R3" t="n">
-        <v>7024990</v>
+        <v>7025133</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>

--- a/artfynd/A 29919-2024 artfynd.xlsx
+++ b/artfynd/A 29919-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120304151</v>
+        <v>120306195</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581524</v>
+        <v>581432</v>
       </c>
       <c r="R2" t="n">
-        <v>7024990</v>
+        <v>7025133</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120306195</v>
+        <v>120304151</v>
       </c>
       <c r="B3" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581432</v>
+        <v>581524</v>
       </c>
       <c r="R3" t="n">
-        <v>7025133</v>
+        <v>7024990</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
